--- a/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
+++ b/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
         <v>2.352502245980863e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>6.469381176447373e-11</v>
+        <v>8.821883422428235e-11</v>
       </c>
       <c r="J3" t="n">
         <v>0.9206680584551148</v>
@@ -599,7 +599,7 @@
         <v>0.0003157673591960714</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000385937883461865</v>
+        <v>0.0004305918534491882</v>
       </c>
       <c r="M3" t="n">
         <v>0.8480769230769231</v>
@@ -608,7 +608,7 @@
         <v>4.222342466243103e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>2.322288356433707e-09</v>
+        <v>3.166756849682327e-09</v>
       </c>
       <c r="P3" t="n">
         <v>0.8828828828828829</v>
@@ -617,7 +617,7 @@
         <v>2.315480778639226e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>8.49009618834383e-13</v>
+        <v>1.157740389319613e-12</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         <v>2.763895092470751e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.34326371673975e-05</v>
+        <v>4.606491820784584e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.8828920570264766</v>
@@ -666,7 +666,7 @@
         <v>8.527014805779314e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.126572095452415e-07</v>
+        <v>3.197630552167243e-07</v>
       </c>
       <c r="P4" t="n">
         <v>0.8575667655786351</v>
@@ -675,7 +675,7 @@
         <v>4.895915153694863e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>8.975844448440583e-07</v>
+        <v>1.223978788423716e-06</v>
       </c>
     </row>
     <row r="5">
@@ -706,7 +706,7 @@
         <v>0.5019569873426638</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6135029845299225</v>
+        <v>0.5791811392415351</v>
       </c>
       <c r="J5" t="n">
         <v>0.8346693386773547</v>
@@ -715,7 +715,7 @@
         <v>0.04443719680108384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04888091648119222</v>
+        <v>0.0555464960013548</v>
       </c>
       <c r="M5" t="n">
         <v>0.8009615384615385</v>
@@ -724,7 +724,7 @@
         <v>0.0005900084461691368</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0008112616134825631</v>
+        <v>0.0008850126692537052</v>
       </c>
       <c r="P5" t="n">
         <v>0.817468105986261</v>
@@ -733,7 +733,7 @@
         <v>0.1067995970246714</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1305328408079318</v>
+        <v>0.1571257328773465</v>
       </c>
     </row>
     <row r="6">
@@ -806,7 +806,7 @@
         <v>8.562936323077191e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.569871659230818e-06</v>
+        <v>1.605550560576973e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.9365482233502538</v>
@@ -815,7 +815,7 @@
         <v>1.127669984450169e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>3.101092457237965e-21</v>
+        <v>4.228762441688134e-21</v>
       </c>
       <c r="M7" t="n">
         <v>0.7096153846153846</v>
@@ -824,7 +824,7 @@
         <v>0.04832921116343653</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04832921116343652</v>
+        <v>0.05576447441934983</v>
       </c>
       <c r="P7" t="n">
         <v>0.8074398249452955</v>
@@ -833,7 +833,7 @@
         <v>0.001001139144887943</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001376566324220922</v>
+        <v>0.001877135896664894</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +864,7 @@
         <v>0.005947489389372665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008177797910387415</v>
+        <v>0.008921234084058999</v>
       </c>
       <c r="J8" t="n">
         <v>0.9502133712660028</v>
@@ -873,7 +873,7 @@
         <v>1.010731856565944e-24</v>
       </c>
       <c r="L8" t="n">
-        <v>3.706016807408461e-24</v>
+        <v>5.053659282829719e-24</v>
       </c>
       <c r="M8" t="n">
         <v>0.6423076923076924</v>
@@ -882,7 +882,7 @@
         <v>1.508019064518737e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>4.147052427426527e-07</v>
+        <v>4.524057193556212e-07</v>
       </c>
       <c r="P8" t="n">
         <v>0.7664945496270796</v>
@@ -891,7 +891,7 @@
         <v>0.8475753501009612</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8475753501009611</v>
+        <v>0.8475753501009612</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>1.049649379879613e-11</v>
       </c>
       <c r="I9" t="n">
-        <v>3.848714392891913e-11</v>
+        <v>5.248246899398064e-11</v>
       </c>
       <c r="J9" t="n">
         <v>0.8790072388831437</v>
@@ -931,7 +931,7 @@
         <v>3.87687132044137e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>8.529116904971014e-09</v>
+        <v>8.307581400945793e-09</v>
       </c>
       <c r="M9" t="n">
         <v>0.8173076923076923</v>
@@ -940,7 +940,7 @@
         <v>0.0001913220486012389</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0003507570891022713</v>
+        <v>0.000358728841127323</v>
       </c>
       <c r="P9" t="n">
         <v>0.8470353761833581</v>
@@ -949,7 +949,7 @@
         <v>2.295058397350061e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>6.311410592712669e-11</v>
+        <v>8.606468990062729e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1022,7 +1022,7 @@
         <v>0.6483318120255308</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7131649932280839</v>
+        <v>0.6946412271702116</v>
       </c>
       <c r="J11" t="n">
         <v>0.8816738816738817</v>
@@ -1031,7 +1031,7 @@
         <v>7.645931260329023e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.155411507823556e-05</v>
+        <v>1.260448917625697e-05</v>
       </c>
       <c r="M11" t="n">
         <v>0.5875</v>
@@ -1040,7 +1040,7 @@
         <v>0.0004067242207159452</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0006391380611250567</v>
+        <v>0.0006778737011932419</v>
       </c>
       <c r="P11" t="n">
         <v>0.705135603000577</v>
@@ -1049,7 +1049,7 @@
         <v>0.2111277101924791</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232240481211727</v>
+        <v>0.2436088963759374</v>
       </c>
     </row>
     <row r="12">
@@ -1080,7 +1080,7 @@
         <v>3.758935090240073e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>8.26965719852816e-09</v>
+        <v>1.127680527072022e-08</v>
       </c>
       <c r="J12" t="n">
         <v>0.6922196796338673</v>
@@ -1089,7 +1089,7 @@
         <v>5.24179716879588e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>9.609961476125781e-07</v>
+        <v>9.828369691492276e-07</v>
       </c>
       <c r="M12" t="n">
         <v>0.5817307692307693</v>
@@ -1098,7 +1098,7 @@
         <v>0.0001434126232102297</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0003155077710625054</v>
+        <v>0.0003073127640219208</v>
       </c>
       <c r="P12" t="n">
         <v>0.632183908045977</v>
@@ -1107,7 +1107,7 @@
         <v>1.053853816781084e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>2.318478396918385e-09</v>
+        <v>3.161561450343253e-09</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
         <v>0.9442746253495373</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9442746253495374</v>
+        <v>0.9442746253495373</v>
       </c>
       <c r="J13" t="n">
         <v>0.7119476268412439</v>
@@ -1147,7 +1147,7 @@
         <v>8.402992784171314e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>1.155411507823556e-05</v>
+        <v>1.260448917625697e-05</v>
       </c>
       <c r="M13" t="n">
         <v>0.8365384615384616</v>
@@ -1156,7 +1156,7 @@
         <v>6.488088653366337e-20</v>
       </c>
       <c r="O13" t="n">
-        <v>7.136897518702971e-19</v>
+        <v>9.732132980049506e-19</v>
       </c>
       <c r="P13" t="n">
         <v>0.7692307692307694</v>
@@ -1165,7 +1165,7 @@
         <v>0.000969738000745019</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001376566324220922</v>
+        <v>0.001877135896664894</v>
       </c>
     </row>
     <row r="14">
@@ -1196,7 +1196,7 @@
         <v>8.609278851316901e-32</v>
       </c>
       <c r="I14" t="n">
-        <v>4.735103368224296e-31</v>
+        <v>6.456959138487676e-31</v>
       </c>
       <c r="J14" t="n">
         <v>0.6167300380228137</v>
@@ -1205,7 +1205,7 @@
         <v>2.753616804890953e-40</v>
       </c>
       <c r="L14" t="n">
-        <v>1.514489242690024e-39</v>
+        <v>2.065212603668215e-39</v>
       </c>
       <c r="M14" t="n">
         <v>0.7798076923076923</v>
@@ -1214,7 +1214,7 @@
         <v>0.024194548970829</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02661400386791191</v>
+        <v>0.03024318621353625</v>
       </c>
       <c r="P14" t="n">
         <v>0.6887473460721868</v>
@@ -1223,7 +1223,7 @@
         <v>8.033070231041609e-16</v>
       </c>
       <c r="R14" t="n">
-        <v>4.418188627072885e-15</v>
+        <v>6.024802673281207e-15</v>
       </c>
     </row>
     <row r="15">
@@ -1254,7 +1254,7 @@
         <v>2.128201710172487e-33</v>
       </c>
       <c r="I15" t="n">
-        <v>2.341021881189736e-32</v>
+        <v>3.192302565258731e-32</v>
       </c>
       <c r="J15" t="n">
         <v>0.6112359550561798</v>
@@ -1263,7 +1263,7 @@
         <v>8.645375519576122e-42</v>
       </c>
       <c r="L15" t="n">
-        <v>9.509913071533733e-41</v>
+        <v>1.296806327936418e-40</v>
       </c>
       <c r="M15" t="n">
         <v>0.7846153846153846</v>
@@ -1272,7 +1272,7 @@
         <v>0.01176620674391631</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01438091935367549</v>
+        <v>0.0160448273780677</v>
       </c>
       <c r="P15" t="n">
         <v>0.6871578947368422</v>
@@ -1281,7 +1281,239 @@
         <v>3.100658082212152e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>3.410723890433367e-15</v>
+        <v>4.650987123318228e-15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B BM25 RAG</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>773</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1101</v>
+      </c>
+      <c r="E16" t="n">
+        <v>259</v>
+      </c>
+      <c r="F16" t="n">
+        <v>267</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7808333333333334</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1275351573374714</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1739115781874609</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.749031007751938</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1172149585573173</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1352480291045969</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7432692307692308</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8011302977838075</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.858353890482651</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.746138996138996</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1920451640875588</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2400564551094485</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B Semantic RAG</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>782</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1109</v>
+      </c>
+      <c r="E17" t="n">
+        <v>251</v>
+      </c>
+      <c r="F17" t="n">
+        <v>258</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7879166666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3538505218171091</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4423131522713864</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7570183930300097</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2480430273894315</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2657603864886766</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7519230769230769</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9192888691574573</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9192888691574573</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7544621321755909</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4887239329852262</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5236327853413137</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B BM25 RAG</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>781</v>
+      </c>
+      <c r="D18" t="n">
+        <v>933</v>
+      </c>
+      <c r="E18" t="n">
+        <v>427</v>
+      </c>
+      <c r="F18" t="n">
+        <v>259</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7141666666666666</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.0206149720666e-07</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.551537430166499e-07</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6465231788079471</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.734438756365958e-14</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.18360968909149e-13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7509615384615385</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.409340315979703e-05</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.523350789949258e-05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.6948398576512456</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.03980311620440691</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.06633852700734484</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B Semantic RAG</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>804</v>
+      </c>
+      <c r="D19" t="n">
+        <v>913</v>
+      </c>
+      <c r="E19" t="n">
+        <v>447</v>
+      </c>
+      <c r="F19" t="n">
+        <v>236</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7154166666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.719899948650225e-07</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.685499889964769e-07</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6426858513189448</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.535286855812015e-15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.960586056743604e-14</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7730769230769231</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.377751313174338e-08</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.688875656587169e-07</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.7018769096464427</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1152255374433874</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1571257328773465</v>
       </c>
     </row>
   </sheetData>

--- a/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
+++ b/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D2" t="n">
         <v>1244</v>
@@ -539,25 +539,25 @@
         <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8375</v>
+        <v>0.8379166666666666</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8684807256235828</v>
+        <v>0.8686296715741789</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7365384615384616</v>
+        <v>0.7375</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.7970863683662851</v>
+        <v>0.797711908476339</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D3" t="n">
         <v>1284</v>
@@ -581,43 +581,43 @@
         <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9025</v>
+        <v>0.9029166666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>2.352502245980863e-11</v>
+        <v>2.207035938454956e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>8.821883422428235e-11</v>
+        <v>8.276384769206086e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9206680584551148</v>
+        <v>0.9207507820646507</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003157673591960714</v>
+        <v>0.0003160912345778657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004305918534491882</v>
+        <v>0.0004310335016970896</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8480769230769231</v>
+        <v>0.8490384615384615</v>
       </c>
       <c r="N3" t="n">
-        <v>4.222342466243103e-10</v>
+        <v>3.934477155453887e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>3.166756849682327e-09</v>
+        <v>2.950857866590415e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8828828828828829</v>
+        <v>0.8834417208604302</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.315480778639226e-13</v>
+        <v>2.159146574448229e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>1.157740389319613e-12</v>
+        <v>1.079573287224114e-12</v>
       </c>
     </row>
     <row r="4">
@@ -645,37 +645,37 @@
         <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>2.763895092470751e-05</v>
+        <v>3.280902437900651e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.606491820784584e-05</v>
+        <v>5.46817072983442e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.8828920570264766</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3605305512221061</v>
+        <v>0.3607633245789883</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3605305512221061</v>
+        <v>0.3607633245789883</v>
       </c>
       <c r="M4" t="n">
         <v>0.8336538461538462</v>
       </c>
       <c r="N4" t="n">
-        <v>8.527014805779314e-08</v>
+        <v>1.120029559232957e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.197630552167243e-07</v>
+        <v>4.200110847123588e-07</v>
       </c>
       <c r="P4" t="n">
         <v>0.8575667655786351</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.895915153694863e-07</v>
+        <v>7.345416629274237e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.223978788423716e-06</v>
+        <v>1.836354157318559e-06</v>
       </c>
     </row>
     <row r="5">
@@ -703,37 +703,37 @@
         <v>0.845</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5019569873426638</v>
+        <v>0.5272215527476609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5791811392415351</v>
+        <v>0.6083325608626857</v>
       </c>
       <c r="J5" t="n">
         <v>0.8346693386773547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04443719680108384</v>
+        <v>0.04441989136440894</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0555464960013548</v>
+        <v>0.05552486420551117</v>
       </c>
       <c r="M5" t="n">
         <v>0.8009615384615385</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005900084461691368</v>
+        <v>0.0007080115956736204</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0008850126692537052</v>
+        <v>0.001062017393510431</v>
       </c>
       <c r="P5" t="n">
         <v>0.817468105986261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1067995970246714</v>
+        <v>0.1157921121265197</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1571257328773465</v>
+        <v>0.1736881681897796</v>
       </c>
     </row>
     <row r="6">
@@ -1031,7 +1031,7 @@
         <v>7.645931260329023e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.260448917625697e-05</v>
+        <v>1.271771987047257e-05</v>
       </c>
       <c r="M11" t="n">
         <v>0.5875</v>
@@ -1049,7 +1049,7 @@
         <v>0.2111277101924791</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2436088963759374</v>
+        <v>0.2639096377405989</v>
       </c>
     </row>
     <row r="12">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D13" t="n">
         <v>1008</v>
@@ -1129,43 +1129,43 @@
         <v>352</v>
       </c>
       <c r="F13" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7825</v>
+        <v>0.7829166666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9442746253495373</v>
+        <v>0.9164681943338163</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9442746253495373</v>
+        <v>0.9164681943338163</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7119476268412439</v>
+        <v>0.7121831561733443</v>
       </c>
       <c r="K13" t="n">
-        <v>8.402992784171314e-06</v>
+        <v>8.478479913648376e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>1.260448917625697e-05</v>
+        <v>1.271771987047257e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8365384615384616</v>
+        <v>0.8375</v>
       </c>
       <c r="N13" t="n">
-        <v>6.488088653366337e-20</v>
+        <v>3.785194724895531e-20</v>
       </c>
       <c r="O13" t="n">
-        <v>9.732132980049506e-19</v>
+        <v>5.677792087343296e-19</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7692307692307694</v>
+        <v>0.7697746354396818</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.000969738000745019</v>
+        <v>0.000849143087229431</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001877135896664894</v>
+        <v>0.001819592329777352</v>
       </c>
     </row>
     <row r="14">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D14" t="n">
         <v>856</v>
@@ -1187,43 +1187,43 @@
         <v>504</v>
       </c>
       <c r="F14" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6945833333333333</v>
+        <v>0.69625</v>
       </c>
       <c r="H14" t="n">
-        <v>8.609278851316901e-32</v>
+        <v>2.354847400284838e-31</v>
       </c>
       <c r="I14" t="n">
-        <v>6.456959138487676e-31</v>
+        <v>1.766135550213628e-30</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6167300380228137</v>
+        <v>0.6178923426838514</v>
       </c>
       <c r="K14" t="n">
-        <v>2.753616804890953e-40</v>
+        <v>5.001791899727602e-40</v>
       </c>
       <c r="L14" t="n">
-        <v>2.065212603668215e-39</v>
+        <v>3.751343924795701e-39</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7798076923076923</v>
+        <v>0.7836538461538461</v>
       </c>
       <c r="N14" t="n">
-        <v>0.024194548970829</v>
+        <v>0.0156861571461071</v>
       </c>
       <c r="O14" t="n">
-        <v>0.03024318621353625</v>
+        <v>0.01960769643263387</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6887473460721868</v>
+        <v>0.6909707503179313</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.033070231041609e-16</v>
+        <v>1.757329480840991e-15</v>
       </c>
       <c r="R14" t="n">
-        <v>6.024802673281207e-15</v>
+        <v>1.317997110630744e-14</v>
       </c>
     </row>
     <row r="15">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D15" t="n">
         <v>841</v>
@@ -1245,43 +1245,43 @@
         <v>519</v>
       </c>
       <c r="F15" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6904166666666667</v>
+        <v>0.6916666666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>2.128201710172487e-33</v>
+        <v>4.093120278424982e-33</v>
       </c>
       <c r="I15" t="n">
-        <v>3.192302565258731e-32</v>
+        <v>6.139680417637474e-32</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6112359550561798</v>
+        <v>0.6121076233183856</v>
       </c>
       <c r="K15" t="n">
-        <v>8.645375519576122e-42</v>
+        <v>9.392660785930085e-42</v>
       </c>
       <c r="L15" t="n">
-        <v>1.296806327936418e-40</v>
+        <v>1.408899117889513e-40</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7846153846153846</v>
+        <v>0.7875</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01176620674391631</v>
+        <v>0.008555088800932555</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0160448273780677</v>
+        <v>0.01166603018308985</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6871578947368422</v>
+        <v>0.6888141295206055</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.100658082212152e-16</v>
+        <v>5.167776432356249e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>4.650987123318228e-15</v>
+        <v>7.751664648534374e-15</v>
       </c>
     </row>
     <row r="16">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D16" t="n">
         <v>1101</v>
@@ -1303,43 +1303,43 @@
         <v>259</v>
       </c>
       <c r="F16" t="n">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7808333333333334</v>
+        <v>0.7825</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1275351573374714</v>
+        <v>0.1663192587342386</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1739115781874609</v>
+        <v>0.2267989891830526</v>
       </c>
       <c r="J16" t="n">
-        <v>0.749031007751938</v>
+        <v>0.75</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1172149585573173</v>
+        <v>0.1300079889956826</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1352480291045969</v>
+        <v>0.1500092180719414</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7432692307692308</v>
+        <v>0.7471153846153846</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8011302977838075</v>
+        <v>0.9597212013213366</v>
       </c>
       <c r="O16" t="n">
-        <v>0.858353890482651</v>
+        <v>0.9597212013213366</v>
       </c>
       <c r="P16" t="n">
-        <v>0.746138996138996</v>
+        <v>0.7485549132947976</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1920451640875588</v>
+        <v>0.2606914862049571</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2400564551094485</v>
+        <v>0.3007978686980274</v>
       </c>
     </row>
     <row r="17">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D17" t="n">
         <v>1109</v>
@@ -1361,43 +1361,43 @@
         <v>251</v>
       </c>
       <c r="F17" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7879166666666667</v>
+        <v>0.7895833333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3538505218171091</v>
+        <v>0.4320586233528336</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4423131522713864</v>
+        <v>0.540073279191042</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7570183930300097</v>
+        <v>0.7579556412729026</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2480430273894315</v>
+        <v>0.2702567913044536</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2657603864886766</v>
+        <v>0.2895608478262002</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7519230769230769</v>
+        <v>0.7557692307692307</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9192888691574573</v>
+        <v>0.7605347198371446</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9192888691574573</v>
+        <v>0.8148586283969407</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7544621321755909</v>
+        <v>0.756860857005296</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4887239329852262</v>
+        <v>0.6094771849016949</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5236327853413137</v>
+        <v>0.6530112695375302</v>
       </c>
     </row>
     <row r="18">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D18" t="n">
         <v>933</v>
@@ -1419,43 +1419,43 @@
         <v>427</v>
       </c>
       <c r="F18" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7141666666666666</v>
+        <v>0.7154166666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0206149720666e-07</v>
+        <v>1.719899948650225e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>2.551537430166499e-07</v>
+        <v>4.299749871625564e-07</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6465231788079471</v>
+        <v>0.6473988439306358</v>
       </c>
       <c r="K18" t="n">
-        <v>4.734438756365958e-14</v>
+        <v>6.904080216455675e-14</v>
       </c>
       <c r="L18" t="n">
-        <v>1.18360968909149e-13</v>
+        <v>1.726020054113919e-13</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7509615384615385</v>
+        <v>0.7538461538461538</v>
       </c>
       <c r="N18" t="n">
-        <v>1.409340315979703e-05</v>
+        <v>6.98466588867629e-06</v>
       </c>
       <c r="O18" t="n">
-        <v>3.523350789949258e-05</v>
+        <v>1.746166472169073e-05</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6948398576512456</v>
+        <v>0.6965792980897378</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.03980311620440691</v>
+        <v>0.05071853054829453</v>
       </c>
       <c r="R18" t="n">
-        <v>0.06633852700734484</v>
+        <v>0.08453088424715755</v>
       </c>
     </row>
     <row r="19">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D19" t="n">
         <v>913</v>
@@ -1477,43 +1477,43 @@
         <v>447</v>
       </c>
       <c r="F19" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7154166666666667</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>1.719899948650225e-07</v>
+        <v>2.874729829856637e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>3.685499889964769e-07</v>
+        <v>6.160135349692793e-07</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6426858513189448</v>
+        <v>0.6435406698564593</v>
       </c>
       <c r="K19" t="n">
-        <v>6.535286855812015e-15</v>
+        <v>9.360933798057072e-15</v>
       </c>
       <c r="L19" t="n">
-        <v>1.960586056743604e-14</v>
+        <v>2.808280139417121e-14</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7730769230769231</v>
+        <v>0.7759615384615385</v>
       </c>
       <c r="N19" t="n">
-        <v>3.377751313174338e-08</v>
+        <v>1.371063677427104e-08</v>
       </c>
       <c r="O19" t="n">
-        <v>1.688875656587169e-07</v>
+        <v>6.855318387135521e-08</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7018769096464427</v>
+        <v>0.7035745422842197</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1152255374433874</v>
+        <v>0.1407463860779056</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1571257328773465</v>
+        <v>0.191926890106235</v>
       </c>
     </row>
   </sheetData>

--- a/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
+++ b/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
         <v>2.207035938454956e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>8.276384769206086e-11</v>
+        <v>8.828143753819825e-11</v>
       </c>
       <c r="J3" t="n">
         <v>0.9207507820646507</v>
@@ -599,7 +599,7 @@
         <v>0.0003160912345778657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004310335016970896</v>
+        <v>0.0004214549794371543</v>
       </c>
       <c r="M3" t="n">
         <v>0.8490384615384615</v>
@@ -608,7 +608,7 @@
         <v>3.934477155453887e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>2.950857866590415e-09</v>
+        <v>2.360686293272333e-09</v>
       </c>
       <c r="P3" t="n">
         <v>0.8834417208604302</v>
@@ -617,7 +617,7 @@
         <v>2.159146574448229e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>1.079573287224114e-12</v>
+        <v>1.295487944668937e-12</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         <v>3.280902437900651e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.46817072983442e-05</v>
+        <v>5.62440417925826e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.8828920570264766</v>
@@ -666,7 +666,7 @@
         <v>1.120029559232957e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>4.200110847123588e-07</v>
+        <v>3.36008867769887e-07</v>
       </c>
       <c r="P4" t="n">
         <v>0.8575667655786351</v>
@@ -675,7 +675,7 @@
         <v>7.345416629274237e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.836354157318559e-06</v>
+        <v>1.762899991025817e-06</v>
       </c>
     </row>
     <row r="5">
@@ -706,7 +706,7 @@
         <v>0.5272215527476609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6083325608626857</v>
+        <v>0.6326658632971931</v>
       </c>
       <c r="J5" t="n">
         <v>0.8346693386773547</v>
@@ -715,7 +715,7 @@
         <v>0.04441989136440894</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05552486420551117</v>
+        <v>0.05330386963729072</v>
       </c>
       <c r="M5" t="n">
         <v>0.8009615384615385</v>
@@ -724,7 +724,7 @@
         <v>0.0007080115956736204</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001062017393510431</v>
+        <v>0.0009440154608981605</v>
       </c>
       <c r="P5" t="n">
         <v>0.817468105986261</v>
@@ -806,7 +806,7 @@
         <v>8.562936323077191e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.605550560576973e-06</v>
+        <v>1.712587264615438e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.9365482233502538</v>
@@ -815,7 +815,7 @@
         <v>1.127669984450169e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>4.228762441688134e-21</v>
+        <v>4.510679937800676e-21</v>
       </c>
       <c r="M7" t="n">
         <v>0.7096153846153846</v>
@@ -824,7 +824,7 @@
         <v>0.04832921116343653</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05576447441934983</v>
+        <v>0.05272277581465803</v>
       </c>
       <c r="P7" t="n">
         <v>0.8074398249452955</v>
@@ -833,7 +833,7 @@
         <v>0.001001139144887943</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001877135896664894</v>
+        <v>0.001716238534093617</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +864,7 @@
         <v>0.005947489389372665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008921234084058999</v>
+        <v>0.008921234084058998</v>
       </c>
       <c r="J8" t="n">
         <v>0.9502133712660028</v>
@@ -873,7 +873,7 @@
         <v>1.010731856565944e-24</v>
       </c>
       <c r="L8" t="n">
-        <v>5.053659282829719e-24</v>
+        <v>6.064391139395664e-24</v>
       </c>
       <c r="M8" t="n">
         <v>0.6423076923076924</v>
@@ -882,7 +882,7 @@
         <v>1.508019064518737e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>4.524057193556212e-07</v>
+        <v>3.619245754844969e-07</v>
       </c>
       <c r="P8" t="n">
         <v>0.7664945496270796</v>
@@ -922,7 +922,7 @@
         <v>1.049649379879613e-11</v>
       </c>
       <c r="I9" t="n">
-        <v>5.248246899398064e-11</v>
+        <v>6.297896279277676e-11</v>
       </c>
       <c r="J9" t="n">
         <v>0.8790072388831437</v>
@@ -931,7 +931,7 @@
         <v>3.87687132044137e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>8.307581400945793e-09</v>
+        <v>9.304491169059289e-09</v>
       </c>
       <c r="M9" t="n">
         <v>0.8173076923076923</v>
@@ -940,7 +940,7 @@
         <v>0.0001913220486012389</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000358728841127323</v>
+        <v>0.000327980654744981</v>
       </c>
       <c r="P9" t="n">
         <v>0.8470353761833581</v>
@@ -949,7 +949,7 @@
         <v>2.295058397350061e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>8.606468990062729e-11</v>
+        <v>9.180233589400247e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1022,7 +1022,7 @@
         <v>0.6483318120255308</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6946412271702116</v>
+        <v>0.7072710676642154</v>
       </c>
       <c r="J11" t="n">
         <v>0.8816738816738817</v>
@@ -1040,7 +1040,7 @@
         <v>0.0004067242207159452</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0006778737011932419</v>
+        <v>0.0006100863310739178</v>
       </c>
       <c r="P11" t="n">
         <v>0.705135603000577</v>
@@ -1049,7 +1049,7 @@
         <v>0.2111277101924791</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2639096377405989</v>
+        <v>0.2533532522309749</v>
       </c>
     </row>
     <row r="12">
@@ -1089,7 +1089,7 @@
         <v>5.24179716879588e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>9.828369691492276e-07</v>
+        <v>1.048359433759176e-06</v>
       </c>
       <c r="M12" t="n">
         <v>0.5817307692307693</v>
@@ -1098,7 +1098,7 @@
         <v>0.0001434126232102297</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0003073127640219208</v>
+        <v>0.0002868252464204594</v>
       </c>
       <c r="P12" t="n">
         <v>0.632183908045977</v>
@@ -1156,7 +1156,7 @@
         <v>3.785194724895531e-20</v>
       </c>
       <c r="O13" t="n">
-        <v>5.677792087343296e-19</v>
+        <v>4.542233669874637e-19</v>
       </c>
       <c r="P13" t="n">
         <v>0.7697746354396818</v>
@@ -1165,7 +1165,7 @@
         <v>0.000849143087229431</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001819592329777352</v>
+        <v>0.001698286174458862</v>
       </c>
     </row>
     <row r="14">
@@ -1174,56 +1174,56 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-4o BM25 RAG</t>
+          <t>GPT-4o RAG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D14" t="n">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="F14" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G14" t="n">
-        <v>0.69625</v>
+        <v>0.6916666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>2.354847400284838e-31</v>
+        <v>4.093120278424982e-33</v>
       </c>
       <c r="I14" t="n">
-        <v>1.766135550213628e-30</v>
+        <v>4.911744334109979e-32</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6178923426838514</v>
+        <v>0.6121076233183856</v>
       </c>
       <c r="K14" t="n">
-        <v>5.001791899727602e-40</v>
+        <v>9.392660785930085e-42</v>
       </c>
       <c r="L14" t="n">
-        <v>3.751343924795701e-39</v>
+        <v>1.12711929431161e-40</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7836538461538461</v>
+        <v>0.7875</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0156861571461071</v>
+        <v>0.008555088800932555</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01960769643263387</v>
+        <v>0.01026610656111907</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6909707503179313</v>
+        <v>0.6888141295206055</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.757329480840991e-15</v>
+        <v>5.167776432356249e-16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.317997110630744e-14</v>
+        <v>6.201331718827499e-15</v>
       </c>
     </row>
     <row r="15">
@@ -1232,56 +1232,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-4o Semantic RAG</t>
+          <t>Llama3.1-70B RAG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D15" t="n">
-        <v>841</v>
+        <v>1109</v>
       </c>
       <c r="E15" t="n">
-        <v>519</v>
+        <v>251</v>
       </c>
       <c r="F15" t="n">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6916666666666667</v>
+        <v>0.7895833333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>4.093120278424982e-33</v>
+        <v>0.4320586233528336</v>
       </c>
       <c r="I15" t="n">
-        <v>6.139680417637474e-32</v>
+        <v>0.5760781644704447</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6121076233183856</v>
+        <v>0.7579556412729026</v>
       </c>
       <c r="K15" t="n">
-        <v>9.392660785930085e-42</v>
+        <v>0.2702567913044536</v>
       </c>
       <c r="L15" t="n">
-        <v>1.408899117889513e-40</v>
+        <v>0.2948255905139494</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7875</v>
+        <v>0.7557692307692307</v>
       </c>
       <c r="N15" t="n">
-        <v>0.008555088800932555</v>
+        <v>0.7605347198371446</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01166603018308985</v>
+        <v>0.7605347198371447</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6888141295206055</v>
+        <v>0.756860857005296</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.167776432356249e-16</v>
+        <v>0.6094771849016949</v>
       </c>
       <c r="R15" t="n">
-        <v>7.751664648534374e-15</v>
+        <v>0.6648842017109399</v>
       </c>
     </row>
     <row r="16">
@@ -1290,230 +1290,56 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Llama3.1-70B BM25 RAG</t>
+          <t>Llama3.1-8B RAG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="D16" t="n">
-        <v>1101</v>
+        <v>913</v>
       </c>
       <c r="E16" t="n">
-        <v>259</v>
+        <v>447</v>
       </c>
       <c r="F16" t="n">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7825</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1663192587342386</v>
+        <v>2.874729829856637e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2267989891830526</v>
+        <v>6.899351591655928e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>0.75</v>
+        <v>0.6435406698564593</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1300079889956826</v>
+        <v>9.360933798057072e-15</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1500092180719414</v>
+        <v>2.808280139417121e-14</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7471153846153846</v>
+        <v>0.7759615384615385</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9597212013213366</v>
+        <v>1.371063677427104e-08</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9597212013213366</v>
+        <v>5.484254709708417e-08</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7485549132947976</v>
+        <v>0.7035745422842197</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2606914862049571</v>
+        <v>0.1407463860779056</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3007978686980274</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B Semantic RAG</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>786</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1109</v>
-      </c>
-      <c r="E17" t="n">
-        <v>251</v>
-      </c>
-      <c r="F17" t="n">
-        <v>254</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.7895833333333333</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4320586233528336</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.540073279191042</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.7579556412729026</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.2702567913044536</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.2895608478262002</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7557692307692307</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.7605347198371446</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.8148586283969407</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.756860857005296</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.6094771849016949</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.6530112695375302</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2400</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B BM25 RAG</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>784</v>
-      </c>
-      <c r="D18" t="n">
-        <v>933</v>
-      </c>
-      <c r="E18" t="n">
-        <v>427</v>
-      </c>
-      <c r="F18" t="n">
-        <v>256</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.7154166666666667</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.719899948650225e-07</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.299749871625564e-07</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.6473988439306358</v>
-      </c>
-      <c r="K18" t="n">
-        <v>6.904080216455675e-14</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.726020054113919e-13</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7538461538461538</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.98466588867629e-06</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.746166472169073e-05</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.6965792980897378</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.05071853054829453</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.08453088424715755</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2400</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B Semantic RAG</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>807</v>
-      </c>
-      <c r="D19" t="n">
-        <v>913</v>
-      </c>
-      <c r="E19" t="n">
-        <v>447</v>
-      </c>
-      <c r="F19" t="n">
-        <v>233</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.7166666666666667</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.874729829856637e-07</v>
-      </c>
-      <c r="I19" t="n">
-        <v>6.160135349692793e-07</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.6435406698564593</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9.360933798057072e-15</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.808280139417121e-14</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.7759615384615385</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.371063677427104e-08</v>
-      </c>
-      <c r="O19" t="n">
-        <v>6.855318387135521e-08</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.7035745422842197</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.1407463860779056</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.191926890106235</v>
+        <v>0.1876618481038742</v>
       </c>
     </row>
   </sheetData>

--- a/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
+++ b/rag/eval/results_full150/evaluation_metrics_fisher_full150.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
